--- a/backend/api/api/domain/data/Account.xlsx
+++ b/backend/api/api/domain/data/Account.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cityd\Documents\GitHub\the-private-ledger\backend\api\api\domain\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6597F55E-6CA2-40C9-BFC7-62887C5D6DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6EEE49-AFD6-47D6-8A8B-574E4EC1703E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{614ABC22-0A8B-4BE8-9481-B0C5D7737119}"/>
+    <workbookView xWindow="4200" yWindow="1755" windowWidth="21600" windowHeight="11295" xr2:uid="{614ABC22-0A8B-4BE8-9481-B0C5D7737119}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -419,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FF24DAC-9579-4B0F-BE65-4B2D8DCA4D98}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -461,8 +461,8 @@
       <c r="C2">
         <v>5</v>
       </c>
-      <c r="D2" s="1">
-        <v>2.5899999999999999E-2</v>
+      <c r="D2">
+        <v>2.59</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -482,8 +482,8 @@
       <c r="C3">
         <v>51.16</v>
       </c>
-      <c r="D3" s="1">
-        <v>0.26490000000000002</v>
+      <c r="D3">
+        <v>26.49</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -503,8 +503,8 @@
       <c r="C4">
         <v>28</v>
       </c>
-      <c r="D4" s="1">
-        <v>0.14499999999999999</v>
+      <c r="D4">
+        <v>14.5</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -524,8 +524,8 @@
       <c r="C5">
         <v>30</v>
       </c>
-      <c r="D5" s="1">
-        <v>0.15529999999999999</v>
+      <c r="D5">
+        <v>15.53</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -545,8 +545,8 @@
       <c r="C6">
         <v>30</v>
       </c>
-      <c r="D6" s="1">
-        <v>0.15529999999999999</v>
+      <c r="D6">
+        <v>15.53</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -566,8 +566,8 @@
       <c r="C7">
         <v>10</v>
       </c>
-      <c r="D7" s="1">
-        <v>5.1799999999999999E-2</v>
+      <c r="D7">
+        <v>5.18</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -587,8 +587,8 @@
       <c r="C8">
         <v>19</v>
       </c>
-      <c r="D8" s="1">
-        <v>9.8400000000000001E-2</v>
+      <c r="D8">
+        <v>9.84</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -608,8 +608,8 @@
       <c r="C9">
         <v>20</v>
       </c>
-      <c r="D9" s="1">
-        <v>0.10349999999999999</v>
+      <c r="D9">
+        <v>10.35</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -618,6 +618,9 @@
         <v>-244.2</v>
       </c>
       <c r="G9" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
